--- a/templates/ERC000018/metadata_template_ERC000018.xlsx
+++ b/templates/ERC000018/metadata_template_ERC000018.xlsx
@@ -23,7 +23,7 @@
     <definedName name="hostsex">'cv_sample'!$BD$1:$BD$17</definedName>
     <definedName name="hysterectomy">'cv_sample'!$BQ$1:$BQ$2</definedName>
     <definedName name="IHMCmedicationcode">'cv_sample'!$AT$1:$AT$22</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$85</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$87</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="891" uniqueCount="868">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="893" uniqueCount="870">
   <si>
     <t>alias</t>
   </si>
@@ -565,6 +565,9 @@
     <t>DNBSEQ-G50</t>
   </si>
   <si>
+    <t>DNBSEQ-G800</t>
+  </si>
+  <si>
     <t>DNBSEQ-T10x4RS</t>
   </si>
   <si>
@@ -728,6 +731,9 @@
   </si>
   <si>
     <t>UG 100</t>
+  </si>
+  <si>
+    <t>Vega</t>
   </si>
   <si>
     <t>instrument_model</t>
@@ -3174,7 +3180,7 @@
         <v>143</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -3218,7 +3224,7 @@
         <v>144</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
   </sheetData>
@@ -3245,7 +3251,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N85"/>
+  <dimension ref="G1:N87"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -3964,6 +3970,16 @@
     </row>
     <row r="85" spans="14:14">
       <c r="N85" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="86" spans="14:14">
+      <c r="N86" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="87" spans="14:14">
+      <c r="N87" t="s">
         <v>117</v>
       </c>
     </row>
@@ -3985,27 +4001,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -4025,122 +4041,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
   </sheetData>
@@ -4164,588 +4180,588 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="BF1" s="1" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="BG1" s="1" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="BH1" s="1" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="BI1" s="1" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="BJ1" s="1" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="BK1" s="1" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="BL1" s="1" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="BM1" s="1" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="BN1" s="1" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="BO1" s="1" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="BP1" s="1" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="BQ1" s="1" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="BR1" s="1" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="BS1" s="1" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="BT1" s="1" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="BU1" s="1" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="BV1" s="1" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="BW1" s="1" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="BX1" s="1" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="BY1" s="1" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="BZ1" s="1" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="CA1" s="1" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="CB1" s="1" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="CC1" s="1" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="CD1" s="1" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="CE1" s="1" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="CF1" s="1" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="CG1" s="1" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="CH1" s="1" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="CI1" s="1" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="CJ1" s="1" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="CK1" s="1" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="CL1" s="1" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="CM1" s="1" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="CN1" s="1" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="CO1" s="1" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="CP1" s="1" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="CQ1" s="1" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="CR1" s="1" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="CS1" s="1" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="CT1" s="1" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
     </row>
     <row r="2" spans="1:98" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AJ2" s="2" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AK2" s="2" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AL2" s="2" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AM2" s="2" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AN2" s="2" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AO2" s="2" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="AP2" s="2" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="AQ2" s="2" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="AR2" s="2" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="AS2" s="2" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="AT2" s="2" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="AU2" s="2" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="AV2" s="2" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="AW2" s="2" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="AX2" s="2" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="AY2" s="2" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="AZ2" s="2" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="BA2" s="2" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="BB2" s="2" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="BC2" s="2" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="BD2" s="2" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="BE2" s="2" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="BF2" s="2" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="BG2" s="2" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="BH2" s="2" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="BI2" s="2" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="BJ2" s="2" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="BK2" s="2" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="BL2" s="2" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="BM2" s="2" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="BN2" s="2" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="BO2" s="2" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="BP2" s="2" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="BQ2" s="2" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="BR2" s="2" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="BS2" s="2" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="BT2" s="2" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="BU2" s="2" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="BV2" s="2" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="BW2" s="2" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="BX2" s="2" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="BY2" s="2" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="BZ2" s="2" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="CA2" s="2" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="CB2" s="2" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="CC2" s="2" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="CD2" s="2" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="CE2" s="2" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="CF2" s="2" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="CG2" s="2" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="CH2" s="2" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="CI2" s="2" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="CJ2" s="2" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="CK2" s="2" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="CL2" s="2" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="CM2" s="2" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="CN2" s="2" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="CO2" s="2" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="CP2" s="2" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="CQ2" s="2" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="CR2" s="2" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="CS2" s="2" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="CT2" s="2" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
     </row>
   </sheetData>
@@ -4795,334 +4811,334 @@
   <sheetData>
     <row r="1" spans="5:69">
       <c r="E1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F1" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="H1" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="O1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="P1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Y1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AO1" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AT1" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="AZ1" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="BD1" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="BQ1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="2" spans="5:69">
       <c r="E2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="H2" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="O2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="P2" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Y2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="AO2" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AT2" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="AZ2" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="BD2" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="BQ2" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="3" spans="5:69">
       <c r="E3" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F3" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="H3" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Y3" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AO3" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AT3" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="AZ3" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="BD3" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
     </row>
     <row r="4" spans="5:69">
       <c r="E4" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F4" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="H4" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AO4" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AT4" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="AZ4" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="BD4" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
     </row>
     <row r="5" spans="5:69">
       <c r="E5" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="F5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="H5" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AO5" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AT5" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="AZ5" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="BD5" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="6" spans="5:69">
       <c r="E6" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H6" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AO6" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AT6" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="AZ6" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="BD6" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
     </row>
     <row r="7" spans="5:69">
       <c r="E7" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="H7" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AO7" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AT7" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="AZ7" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="BD7" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
     </row>
     <row r="8" spans="5:69">
       <c r="E8" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AO8" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AT8" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="AZ8" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="BD8" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
     </row>
     <row r="9" spans="5:69">
       <c r="E9" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AO9" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AT9" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="AZ9" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="BD9" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
     </row>
     <row r="10" spans="5:69">
       <c r="E10" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AO10" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AT10" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="AZ10" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="BD10" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
     </row>
     <row r="11" spans="5:69">
       <c r="E11" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AO11" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AT11" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="AZ11" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="BD11" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
     </row>
     <row r="12" spans="5:69">
       <c r="E12" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AO12" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AT12" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="AZ12" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="BD12" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
     </row>
     <row r="13" spans="5:69">
       <c r="E13" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AO13" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AT13" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="AZ13" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="BD13" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
     </row>
     <row r="14" spans="5:69">
       <c r="E14" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AO14" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AT14" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="AZ14" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="BD14" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
     </row>
     <row r="15" spans="5:69">
       <c r="E15" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AO15" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AT15" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="AZ15" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="BD15" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
     </row>
     <row r="16" spans="5:69">
       <c r="E16" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AO16" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AT16" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="AZ16" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="BD16" t="s">
         <v>116</v>
@@ -5130,1526 +5146,1526 @@
     </row>
     <row r="17" spans="5:56">
       <c r="E17" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AO17" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AT17" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="AZ17" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="BD17" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
     </row>
     <row r="18" spans="5:56">
       <c r="E18" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AO18" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AT18" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="AZ18" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
     </row>
     <row r="19" spans="5:56">
       <c r="E19" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AO19" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AT19" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="AZ19" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
     </row>
     <row r="20" spans="5:56">
       <c r="E20" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AO20" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AT20" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="AZ20" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
     </row>
     <row r="21" spans="5:56">
       <c r="E21" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AO21" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AT21" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="AZ21" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
     </row>
     <row r="22" spans="5:56">
       <c r="E22" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AO22" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AT22" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="AZ22" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
     </row>
     <row r="23" spans="5:56">
       <c r="E23" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AO23" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AZ23" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
     </row>
     <row r="24" spans="5:56">
       <c r="E24" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AO24" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AZ24" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="25" spans="5:56">
       <c r="E25" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AO25" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AZ25" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
     </row>
     <row r="26" spans="5:56">
       <c r="E26" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AO26" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AZ26" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
     </row>
     <row r="27" spans="5:56">
       <c r="E27" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AO27" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AZ27" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
     </row>
     <row r="28" spans="5:56">
       <c r="E28" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AO28" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AZ28" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
     </row>
     <row r="29" spans="5:56">
       <c r="E29" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AO29" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AZ29" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
     </row>
     <row r="30" spans="5:56">
       <c r="E30" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AO30" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AZ30" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
     </row>
     <row r="31" spans="5:56">
       <c r="AO31" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AZ31" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
     </row>
     <row r="32" spans="5:56">
       <c r="AO32" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AZ32" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
     </row>
     <row r="33" spans="41:52">
       <c r="AO33" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AZ33" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
     </row>
     <row r="34" spans="41:52">
       <c r="AO34" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AZ34" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
     </row>
     <row r="35" spans="41:52">
       <c r="AO35" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AZ35" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
     </row>
     <row r="36" spans="41:52">
       <c r="AO36" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AZ36" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
     </row>
     <row r="37" spans="41:52">
       <c r="AO37" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AZ37" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
     </row>
     <row r="38" spans="41:52">
       <c r="AO38" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AZ38" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
     </row>
     <row r="39" spans="41:52">
       <c r="AO39" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AZ39" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
     </row>
     <row r="40" spans="41:52">
       <c r="AO40" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AZ40" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
     </row>
     <row r="41" spans="41:52">
       <c r="AO41" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AZ41" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
     </row>
     <row r="42" spans="41:52">
       <c r="AO42" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AZ42" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
     </row>
     <row r="43" spans="41:52">
       <c r="AO43" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AZ43" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
     </row>
     <row r="44" spans="41:52">
       <c r="AO44" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AZ44" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
     </row>
     <row r="45" spans="41:52">
       <c r="AO45" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AZ45" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
     </row>
     <row r="46" spans="41:52">
       <c r="AO46" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="AZ46" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
     </row>
     <row r="47" spans="41:52">
       <c r="AO47" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AZ47" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
     </row>
     <row r="48" spans="41:52">
       <c r="AO48" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AZ48" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
     </row>
     <row r="49" spans="41:41">
       <c r="AO49" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="50" spans="41:41">
       <c r="AO50" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="51" spans="41:41">
       <c r="AO51" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="52" spans="41:41">
       <c r="AO52" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="53" spans="41:41">
       <c r="AO53" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="54" spans="41:41">
       <c r="AO54" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="55" spans="41:41">
       <c r="AO55" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="56" spans="41:41">
       <c r="AO56" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="57" spans="41:41">
       <c r="AO57" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="58" spans="41:41">
       <c r="AO58" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="59" spans="41:41">
       <c r="AO59" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="60" spans="41:41">
       <c r="AO60" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="61" spans="41:41">
       <c r="AO61" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="62" spans="41:41">
       <c r="AO62" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="63" spans="41:41">
       <c r="AO63" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="64" spans="41:41">
       <c r="AO64" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="65" spans="41:41">
       <c r="AO65" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="66" spans="41:41">
       <c r="AO66" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="67" spans="41:41">
       <c r="AO67" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="68" spans="41:41">
       <c r="AO68" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="69" spans="41:41">
       <c r="AO69" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="70" spans="41:41">
       <c r="AO70" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="71" spans="41:41">
       <c r="AO71" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="72" spans="41:41">
       <c r="AO72" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="73" spans="41:41">
       <c r="AO73" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="74" spans="41:41">
       <c r="AO74" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="75" spans="41:41">
       <c r="AO75" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="76" spans="41:41">
       <c r="AO76" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="77" spans="41:41">
       <c r="AO77" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="78" spans="41:41">
       <c r="AO78" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="79" spans="41:41">
       <c r="AO79" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="80" spans="41:41">
       <c r="AO80" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="81" spans="41:41">
       <c r="AO81" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="82" spans="41:41">
       <c r="AO82" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="83" spans="41:41">
       <c r="AO83" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="84" spans="41:41">
       <c r="AO84" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="85" spans="41:41">
       <c r="AO85" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="86" spans="41:41">
       <c r="AO86" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="87" spans="41:41">
       <c r="AO87" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="88" spans="41:41">
       <c r="AO88" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="89" spans="41:41">
       <c r="AO89" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="90" spans="41:41">
       <c r="AO90" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="91" spans="41:41">
       <c r="AO91" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="92" spans="41:41">
       <c r="AO92" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="93" spans="41:41">
       <c r="AO93" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="94" spans="41:41">
       <c r="AO94" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="95" spans="41:41">
       <c r="AO95" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="96" spans="41:41">
       <c r="AO96" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="97" spans="41:41">
       <c r="AO97" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="98" spans="41:41">
       <c r="AO98" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="99" spans="41:41">
       <c r="AO99" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="100" spans="41:41">
       <c r="AO100" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="101" spans="41:41">
       <c r="AO101" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="102" spans="41:41">
       <c r="AO102" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="103" spans="41:41">
       <c r="AO103" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="104" spans="41:41">
       <c r="AO104" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="105" spans="41:41">
       <c r="AO105" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="106" spans="41:41">
       <c r="AO106" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="107" spans="41:41">
       <c r="AO107" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="108" spans="41:41">
       <c r="AO108" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="109" spans="41:41">
       <c r="AO109" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="110" spans="41:41">
       <c r="AO110" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="111" spans="41:41">
       <c r="AO111" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="112" spans="41:41">
       <c r="AO112" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="113" spans="41:41">
       <c r="AO113" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="114" spans="41:41">
       <c r="AO114" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="115" spans="41:41">
       <c r="AO115" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="116" spans="41:41">
       <c r="AO116" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="117" spans="41:41">
       <c r="AO117" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="118" spans="41:41">
       <c r="AO118" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="119" spans="41:41">
       <c r="AO119" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="120" spans="41:41">
       <c r="AO120" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="121" spans="41:41">
       <c r="AO121" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="122" spans="41:41">
       <c r="AO122" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="123" spans="41:41">
       <c r="AO123" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="124" spans="41:41">
       <c r="AO124" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="125" spans="41:41">
       <c r="AO125" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="126" spans="41:41">
       <c r="AO126" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="127" spans="41:41">
       <c r="AO127" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="128" spans="41:41">
       <c r="AO128" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="129" spans="41:41">
       <c r="AO129" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="130" spans="41:41">
       <c r="AO130" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="131" spans="41:41">
       <c r="AO131" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="132" spans="41:41">
       <c r="AO132" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="133" spans="41:41">
       <c r="AO133" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="134" spans="41:41">
       <c r="AO134" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="135" spans="41:41">
       <c r="AO135" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="136" spans="41:41">
       <c r="AO136" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="137" spans="41:41">
       <c r="AO137" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="138" spans="41:41">
       <c r="AO138" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="139" spans="41:41">
       <c r="AO139" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="140" spans="41:41">
       <c r="AO140" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="141" spans="41:41">
       <c r="AO141" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="142" spans="41:41">
       <c r="AO142" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="143" spans="41:41">
       <c r="AO143" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="144" spans="41:41">
       <c r="AO144" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="145" spans="41:41">
       <c r="AO145" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="146" spans="41:41">
       <c r="AO146" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="147" spans="41:41">
       <c r="AO147" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="148" spans="41:41">
       <c r="AO148" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="149" spans="41:41">
       <c r="AO149" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="150" spans="41:41">
       <c r="AO150" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="151" spans="41:41">
       <c r="AO151" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="152" spans="41:41">
       <c r="AO152" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="153" spans="41:41">
       <c r="AO153" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="154" spans="41:41">
       <c r="AO154" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="155" spans="41:41">
       <c r="AO155" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="156" spans="41:41">
       <c r="AO156" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="157" spans="41:41">
       <c r="AO157" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="158" spans="41:41">
       <c r="AO158" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="159" spans="41:41">
       <c r="AO159" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="160" spans="41:41">
       <c r="AO160" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="161" spans="41:41">
       <c r="AO161" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="162" spans="41:41">
       <c r="AO162" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="163" spans="41:41">
       <c r="AO163" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="164" spans="41:41">
       <c r="AO164" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="165" spans="41:41">
       <c r="AO165" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="166" spans="41:41">
       <c r="AO166" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="167" spans="41:41">
       <c r="AO167" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="168" spans="41:41">
       <c r="AO168" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="169" spans="41:41">
       <c r="AO169" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="170" spans="41:41">
       <c r="AO170" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="171" spans="41:41">
       <c r="AO171" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="172" spans="41:41">
       <c r="AO172" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="173" spans="41:41">
       <c r="AO173" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="174" spans="41:41">
       <c r="AO174" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="175" spans="41:41">
       <c r="AO175" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="176" spans="41:41">
       <c r="AO176" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="177" spans="41:41">
       <c r="AO177" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="178" spans="41:41">
       <c r="AO178" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="179" spans="41:41">
       <c r="AO179" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="180" spans="41:41">
       <c r="AO180" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="181" spans="41:41">
       <c r="AO181" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="182" spans="41:41">
       <c r="AO182" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="183" spans="41:41">
       <c r="AO183" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="184" spans="41:41">
       <c r="AO184" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="185" spans="41:41">
       <c r="AO185" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="186" spans="41:41">
       <c r="AO186" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="187" spans="41:41">
       <c r="AO187" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="188" spans="41:41">
       <c r="AO188" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="189" spans="41:41">
       <c r="AO189" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="190" spans="41:41">
       <c r="AO190" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="191" spans="41:41">
       <c r="AO191" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="192" spans="41:41">
       <c r="AO192" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="193" spans="41:41">
       <c r="AO193" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="194" spans="41:41">
       <c r="AO194" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="195" spans="41:41">
       <c r="AO195" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="196" spans="41:41">
       <c r="AO196" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="197" spans="41:41">
       <c r="AO197" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="198" spans="41:41">
       <c r="AO198" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="199" spans="41:41">
       <c r="AO199" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="200" spans="41:41">
       <c r="AO200" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="201" spans="41:41">
       <c r="AO201" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="202" spans="41:41">
       <c r="AO202" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="203" spans="41:41">
       <c r="AO203" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="204" spans="41:41">
       <c r="AO204" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="205" spans="41:41">
       <c r="AO205" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="206" spans="41:41">
       <c r="AO206" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="207" spans="41:41">
       <c r="AO207" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="208" spans="41:41">
       <c r="AO208" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="209" spans="41:41">
       <c r="AO209" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="210" spans="41:41">
       <c r="AO210" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="211" spans="41:41">
       <c r="AO211" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="212" spans="41:41">
       <c r="AO212" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="213" spans="41:41">
       <c r="AO213" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="214" spans="41:41">
       <c r="AO214" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="215" spans="41:41">
       <c r="AO215" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="216" spans="41:41">
       <c r="AO216" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="217" spans="41:41">
       <c r="AO217" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="218" spans="41:41">
       <c r="AO218" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="219" spans="41:41">
       <c r="AO219" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
     </row>
     <row r="220" spans="41:41">
       <c r="AO220" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="221" spans="41:41">
       <c r="AO221" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="222" spans="41:41">
       <c r="AO222" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
     <row r="223" spans="41:41">
       <c r="AO223" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="224" spans="41:41">
       <c r="AO224" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="225" spans="41:41">
       <c r="AO225" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="226" spans="41:41">
       <c r="AO226" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="227" spans="41:41">
       <c r="AO227" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
     </row>
     <row r="228" spans="41:41">
       <c r="AO228" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
     </row>
     <row r="229" spans="41:41">
       <c r="AO229" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
     </row>
     <row r="230" spans="41:41">
       <c r="AO230" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="231" spans="41:41">
       <c r="AO231" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
     </row>
     <row r="232" spans="41:41">
       <c r="AO232" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
     </row>
     <row r="233" spans="41:41">
       <c r="AO233" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
     </row>
     <row r="234" spans="41:41">
       <c r="AO234" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
     </row>
     <row r="235" spans="41:41">
       <c r="AO235" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
     </row>
     <row r="236" spans="41:41">
       <c r="AO236" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="237" spans="41:41">
       <c r="AO237" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
     </row>
     <row r="238" spans="41:41">
       <c r="AO238" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="239" spans="41:41">
       <c r="AO239" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
     </row>
     <row r="240" spans="41:41">
       <c r="AO240" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
     </row>
     <row r="241" spans="41:41">
       <c r="AO241" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
     </row>
     <row r="242" spans="41:41">
       <c r="AO242" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
     </row>
     <row r="243" spans="41:41">
       <c r="AO243" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
     </row>
     <row r="244" spans="41:41">
       <c r="AO244" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
     </row>
     <row r="245" spans="41:41">
       <c r="AO245" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
     </row>
     <row r="246" spans="41:41">
       <c r="AO246" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
     </row>
     <row r="247" spans="41:41">
       <c r="AO247" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
     </row>
     <row r="248" spans="41:41">
       <c r="AO248" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
     </row>
     <row r="249" spans="41:41">
       <c r="AO249" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
     </row>
     <row r="250" spans="41:41">
       <c r="AO250" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
     </row>
     <row r="251" spans="41:41">
       <c r="AO251" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
     </row>
     <row r="252" spans="41:41">
       <c r="AO252" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
     </row>
     <row r="253" spans="41:41">
       <c r="AO253" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
     </row>
     <row r="254" spans="41:41">
       <c r="AO254" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
     </row>
     <row r="255" spans="41:41">
       <c r="AO255" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
     </row>
     <row r="256" spans="41:41">
       <c r="AO256" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
     <row r="257" spans="41:41">
       <c r="AO257" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
     </row>
     <row r="258" spans="41:41">
       <c r="AO258" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
     </row>
     <row r="259" spans="41:41">
       <c r="AO259" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
     </row>
     <row r="260" spans="41:41">
       <c r="AO260" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
     </row>
     <row r="261" spans="41:41">
       <c r="AO261" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
     </row>
     <row r="262" spans="41:41">
       <c r="AO262" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
     </row>
     <row r="263" spans="41:41">
       <c r="AO263" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="264" spans="41:41">
       <c r="AO264" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="265" spans="41:41">
       <c r="AO265" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="266" spans="41:41">
       <c r="AO266" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
     </row>
     <row r="267" spans="41:41">
       <c r="AO267" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
     </row>
     <row r="268" spans="41:41">
       <c r="AO268" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
     </row>
     <row r="269" spans="41:41">
       <c r="AO269" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
     </row>
     <row r="270" spans="41:41">
       <c r="AO270" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
     </row>
     <row r="271" spans="41:41">
       <c r="AO271" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
     </row>
     <row r="272" spans="41:41">
       <c r="AO272" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
     </row>
     <row r="273" spans="41:41">
       <c r="AO273" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
     </row>
     <row r="274" spans="41:41">
       <c r="AO274" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="275" spans="41:41">
       <c r="AO275" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
     </row>
     <row r="276" spans="41:41">
       <c r="AO276" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="277" spans="41:41">
       <c r="AO277" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
     </row>
     <row r="278" spans="41:41">
       <c r="AO278" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
     </row>
     <row r="279" spans="41:41">
       <c r="AO279" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="280" spans="41:41">
       <c r="AO280" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
     </row>
     <row r="281" spans="41:41">
       <c r="AO281" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
     </row>
     <row r="282" spans="41:41">
       <c r="AO282" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
     </row>
     <row r="283" spans="41:41">
       <c r="AO283" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
     </row>
     <row r="284" spans="41:41">
       <c r="AO284" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
     </row>
     <row r="285" spans="41:41">
       <c r="AO285" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
     </row>
     <row r="286" spans="41:41">
       <c r="AO286" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
     </row>
     <row r="287" spans="41:41">
       <c r="AO287" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
     </row>
     <row r="288" spans="41:41">
       <c r="AO288" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
     </row>
     <row r="289" spans="41:41">
       <c r="AO289" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000018/metadata_template_ERC000018.xlsx
+++ b/templates/ERC000018/metadata_template_ERC000018.xlsx
@@ -18,12 +18,12 @@
   </sheets>
   <definedNames>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
-    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$AO$1:$AO$289</definedName>
+    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$AO$1:$AO$294</definedName>
     <definedName name="hostoccupation">'cv_sample'!$AZ$1:$AZ$48</definedName>
     <definedName name="hostsex">'cv_sample'!$BD$1:$BD$17</definedName>
     <definedName name="hysterectomy">'cv_sample'!$BQ$1:$BQ$2</definedName>
-    <definedName name="IHMCmedicationcode">'cv_sample'!$AT$1:$AT$22</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$86</definedName>
+    <definedName name="ihmcmedicationcode">'cv_sample'!$AT$1:$AT$22</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$87</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="892" uniqueCount="869">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="898" uniqueCount="875">
   <si>
     <t>alias</t>
   </si>
@@ -565,6 +565,9 @@
     <t>DNBSEQ-G50</t>
   </si>
   <si>
+    <t>DNBSEQ-G800</t>
+  </si>
+  <si>
     <t>DNBSEQ-T10x4RS</t>
   </si>
   <si>
@@ -940,7 +943,7 @@
     <t>phototroph</t>
   </si>
   <si>
-    <t>trophic level</t>
+    <t>trophic_level</t>
   </si>
   <si>
     <t>(Optional) Trophic levels are the feeding position in a food chain. microbes can be a range of producers (e.g. chemolithotroph)</t>
@@ -961,13 +964,13 @@
     <t>symbiont</t>
   </si>
   <si>
-    <t>observed biotic relationship</t>
+    <t>observed_biotic_relationship</t>
   </si>
   <si>
     <t>(Optional) Description of relationship(s) between the subject organism and other organism(s) it is associated with. e.g., parasite on species x; mutualist with species y. the target organism is the subject of the relationship, and the other organism(s) is the object.</t>
   </si>
   <si>
-    <t>known pathogenicity</t>
+    <t>known_pathogenicity</t>
   </si>
   <si>
     <t>(Optional) To what is the entity pathogenic, for instance plant, fungi, bacteria</t>
@@ -994,7 +997,7 @@
     <t>obligate anaerobe</t>
   </si>
   <si>
-    <t>relationship to oxygen</t>
+    <t>relationship_to_oxygen</t>
   </si>
   <si>
     <t>(Optional) Is this organism an aerobe, anaerobe? please note that aerobic and anaerobic are valid descriptors for microbial environments</t>
@@ -1006,31 +1009,31 @@
     <t>(Optional) The type of reproduction from the parent stock. values for this field is specific to different taxa. for phage or virus: lytic/lysogenic/temperate/obligately lytic. for plasmids: incompatibility group. for eukaryotes: sexual/asexual. mandatory for migs of eukayotes, plasmids and viruses.</t>
   </si>
   <si>
-    <t>observed host symbionts</t>
+    <t>observed_host_symbionts</t>
   </si>
   <si>
     <t>(Optional) The taxonomic name of the organism(s) found living in mutualistic, commensalistic, or parasitic symbiosis with the specific host.</t>
   </si>
   <si>
-    <t>sample collection device</t>
+    <t>sample_collection_device</t>
   </si>
   <si>
     <t>(Optional) The device used to collect an environmental sample. it is recommended to use terms listed under environmental sampling device (http://purl.obolibrary.org/obo/envo) and/or terms listed under specimen collection device (http://purl.obolibrary.org/obo/genepio_0002094).</t>
   </si>
   <si>
-    <t>sample collection method</t>
+    <t>sample_collection_method</t>
   </si>
   <si>
     <t>(Optional) The method employed for collecting the sample. can be provided in the form of a pmid, doi, url or text.</t>
   </si>
   <si>
-    <t>sample storage temperature</t>
+    <t>sample_storage_temperature</t>
   </si>
   <si>
     <t>(Optional) Temperature at which sample was stored, e.g. -80 (Units: °C)</t>
   </si>
   <si>
-    <t>sample storage location</t>
+    <t>sample_storage_location</t>
   </si>
   <si>
     <t>(Optional) Location at which sample was stored, usually name of a specific freezer/room. indicate the location name.</t>
@@ -1042,7 +1045,7 @@
     <t>anaerobic</t>
   </si>
   <si>
-    <t>oxygenation status of sample</t>
+    <t>oxygenation_status_of_sample</t>
   </si>
   <si>
     <t>(Optional) Oxygenation status of sample</t>
@@ -1054,13 +1057,13 @@
     <t>Yes</t>
   </si>
   <si>
-    <t>medical history performed</t>
+    <t>medical_history_performed</t>
   </si>
   <si>
     <t>(Optional) Whether full medical history was collected</t>
   </si>
   <si>
-    <t>project name</t>
+    <t>project_name</t>
   </si>
   <si>
     <t>(Mandatory) Name of the project within which the sequencing was organized</t>
@@ -1072,37 +1075,37 @@
     <t>(Optional) The ploidy level of the genome (e.g. allopolyploid, haploid, diploid, triploid, tetraploid). it has implications for the downstream study of duplicated gene and regions of the genomes (and perhaps for difficulties in assembly). for terms, please select terms listed under class ploidy (pato:001374) of phenotypic quality ontology (pato), and for a browser of pato (v 2018-03-27) please refer to http://purl.bioontology.org/ontology/pato</t>
   </si>
   <si>
-    <t>number of replicons</t>
+    <t>number_of_replicons</t>
   </si>
   <si>
     <t>(Optional) Reports the number of replicons in a nuclear genome of eukaryotes, in the genome of a bacterium or archaea or the number of segments in a segmented virus. always applied to the haploid chromosome count of a eukaryote. mandatory for migs of eukaryotes, bacteria, archaea and segmented virus.</t>
   </si>
   <si>
-    <t>extrachromosomal elements</t>
+    <t>extrachromosomal_elements</t>
   </si>
   <si>
     <t>(Optional) Do plasmids exist of significant phenotypic consequence (e.g. ones that determine virulence or antibiotic resistance). megaplasmids? other plasmids (borrelia has 15+ plasmids).</t>
   </si>
   <si>
-    <t>estimated size</t>
+    <t>estimated_size</t>
   </si>
   <si>
     <t>(Optional) The estimated size of the genome (in bp) prior to sequencing. of particular importance in the sequencing of (eukaryotic) genome which could remain in draft form for a long or unspecified period. mandatory for migs of eukaryotes.</t>
   </si>
   <si>
-    <t>target gene</t>
+    <t>target_gene</t>
   </si>
   <si>
     <t>(Optional) Targeted gene or locus name for marker gene studies</t>
   </si>
   <si>
-    <t>target subfragment</t>
+    <t>target_subfragment</t>
   </si>
   <si>
     <t>(Optional) Name of subfragment of a gene or locus. important to e.g. identify special regions on marker genes like v6 on 16s rrna</t>
   </si>
   <si>
-    <t>multiplex identifiers</t>
+    <t>multiplex_identifiers</t>
   </si>
   <si>
     <t>(Optional) Molecular barcodes, called multiplex identifiers (mids), that are used to specifically tag unique samples in a sequencing run. sequence should be reported in uppercase letters</t>
@@ -1117,31 +1120,31 @@
     <t>software</t>
   </si>
   <si>
-    <t>sequence quality check</t>
+    <t>sequence_quality_check</t>
   </si>
   <si>
     <t>(Optional) Indicate if the sequence has been called by automatic systems (none) or undergone a manual editing procedure (e.g. by inspecting the raw data or chromatograms). applied only for sequences that are not submitted to sra or dra</t>
   </si>
   <si>
-    <t>chimera check software</t>
+    <t>chimera_check_software</t>
   </si>
   <si>
     <t>(Optional) Tool(s) used for chimera checking, including version number and parameters, to discover and remove chimeric sequences. a chimeric sequence is comprised of two or more phylogenetically distinct parent sequences.</t>
   </si>
   <si>
-    <t>relevant electronic resources</t>
+    <t>relevant_electronic_resources</t>
   </si>
   <si>
     <t>(Optional) A related resource that is referenced, cited, or otherwise associated to the sequence in the format of a pmid, doi or url</t>
   </si>
   <si>
-    <t>relevant standard operating procedures</t>
+    <t>relevant_standard_operating_procedures</t>
   </si>
   <si>
     <t>(Optional) Standard operating procedures used in assembly and/or annotation of genomes, metagenomes or environmental sequences in the format of a pmid, doi or url</t>
   </si>
   <si>
-    <t>collection date</t>
+    <t>collection_date</t>
   </si>
   <si>
     <t>(Mandatory) The date the sample was collected with the intention of sequencing, either as an instance (single point in time) or interval. in case no exact time is available, the date/time can be right truncated i.e. all of these are valid iso8601 compliant times: 2008-01-23t19:23:10+00:00; 2008-01-23t19:23:10; 2008-01-23; 2008-01; 2008.</t>
@@ -1153,37 +1156,37 @@
     <t>(Optional) The altitude of the sample is the vertical distance between earth's surface above sea level and the sampled position in the air. (Units: m)</t>
   </si>
   <si>
-    <t>geographic location (latitude)</t>
+    <t>geographic_location_latitude</t>
   </si>
   <si>
     <t>(Mandatory) The geographical origin of the sample as defined by latitude. the values should be reported in decimal degrees and in wgs84 system (Units: DD)</t>
   </si>
   <si>
-    <t>geographic location (longitude)</t>
+    <t>geographic_location_longitude</t>
   </si>
   <si>
     <t>(Mandatory) The geographical origin of the sample as defined by longitude. the values should be reported in decimal degrees and in wgs84 system (Units: DD)</t>
   </si>
   <si>
-    <t>geographic location (region and locality)</t>
+    <t>geographic_location_region_and_locality</t>
   </si>
   <si>
     <t>(Optional) The geographical origin of the sample as defined by the specific region name followed by the locality name.</t>
   </si>
   <si>
-    <t>broad-scale environmental context</t>
+    <t>broadscale_environmental_context</t>
   </si>
   <si>
     <t>(Mandatory) Report the major environmental system the sample or specimen came from. the system(s) identified should have a coarse spatial grain, to provide the general environmental context of where the sampling was done (e.g. in the desert or a rainforest). we recommend using subclasses of envo’s biome class: http://purl.obolibrary.org/obo/envo_00000428. envo documentation about how to use the field: https://github.com/environmentontology/envo/wiki/using-envo-with-mixs.</t>
   </si>
   <si>
-    <t>local environmental context</t>
+    <t>local_environmental_context</t>
   </si>
   <si>
     <t>(Mandatory) Report the entity or entities which are in the sample or specimen’s local vicinity and which you believe have significant causal influences on your sample or specimen. we recommend using envo terms which are of smaller spatial grain than your entry for "broad-scale environmental context". terms, such as anatomical sites, from other obo library ontologies which interoperate with envo (e.g. uberon) are accepted in this field. envo documentation about how to use the field: https://github.com/environmentontology/envo/wiki/using-envo-with-mixs.</t>
   </si>
   <si>
-    <t>environmental medium</t>
+    <t>environmental_medium</t>
   </si>
   <si>
     <t>(Mandatory) Report the environmental material(s) immediately surrounding the sample or specimen at the time of sampling. we recommend using subclasses of 'environmental material' (http://purl.obolibrary.org/obo/envo_00010483). envo documentation about how to use the field: https://github.com/environmentontology/envo/wiki/using-envo-with-mixs . terms from other obo ontologies are permissible as long as they reference mass/volume nouns (e.g. air, water, blood) and not discrete, countable entities (e.g. a tree, a leaf, a table top).</t>
@@ -1195,19 +1198,19 @@
     <t>(Optional) The elevation of the sampling site as measured by the vertical distance from mean sea level. (Units: m)</t>
   </si>
   <si>
-    <t>amount or size of sample collected</t>
-  </si>
-  <si>
-    <t>(Optional) The total amount or size (volume (ml), mass (g) or area (m2) ) of sample collected. (Units: m3)</t>
-  </si>
-  <si>
-    <t>organism count</t>
+    <t>amount_or_size_of_sample_collected</t>
+  </si>
+  <si>
+    <t>(Optional) The total amount or size (volume (ml), mass (g) or area (m2) ) of sample collected. (Units: kg)</t>
+  </si>
+  <si>
+    <t>organism_count</t>
   </si>
   <si>
     <t>(Optional) Total cell count of any organism (or group of organisms) per gram, volume or area of sample, should include name of organism followed by count. the method that was used for the enumeration (e.g. qpcr, atp, mpn, etc.) should also be provided. (example: total prokaryotes; 3.5e7 cells per ml; qpcr)</t>
   </si>
   <si>
-    <t>sample storage duration</t>
+    <t>sample_storage_duration</t>
   </si>
   <si>
     <t>(Optional) Duration for which the sample was stored. indicate the duration for which the sample was stored written in iso 8601 format.</t>
@@ -1426,9 +1429,6 @@
     <t>Dominican Republic</t>
   </si>
   <si>
-    <t>East Timor</t>
-  </si>
-  <si>
     <t>Ecuador</t>
   </si>
   <si>
@@ -1447,6 +1447,9 @@
     <t>Estonia</t>
   </si>
   <si>
+    <t>Eswatini</t>
+  </si>
+  <si>
     <t>Ethiopia</t>
   </si>
   <si>
@@ -1648,6 +1651,9 @@
     <t>Liechtenstein</t>
   </si>
   <si>
+    <t>Line Islands</t>
+  </si>
+  <si>
     <t>Lithuania</t>
   </si>
   <si>
@@ -1657,9 +1663,6 @@
     <t>Macau</t>
   </si>
   <si>
-    <t>Macedonia</t>
-  </si>
-  <si>
     <t>Madagascar</t>
   </si>
   <si>
@@ -1699,7 +1702,7 @@
     <t>Mexico</t>
   </si>
   <si>
-    <t>Micronesia</t>
+    <t>Micronesia, Federated States of</t>
   </si>
   <si>
     <t>Midway Islands</t>
@@ -1768,6 +1771,9 @@
     <t>North Korea</t>
   </si>
   <si>
+    <t>North Macedonia</t>
+  </si>
+  <si>
     <t>North Sea</t>
   </si>
   <si>
@@ -1843,6 +1849,9 @@
     <t>Rwanda</t>
   </si>
   <si>
+    <t>Saint Barthelemy</t>
+  </si>
+  <si>
     <t>Saint Helena</t>
   </si>
   <si>
@@ -1864,6 +1873,9 @@
     <t>San Marino</t>
   </si>
   <si>
+    <t>Saint Martin</t>
+  </si>
+  <si>
     <t>Sao Tome and Principe</t>
   </si>
   <si>
@@ -1909,6 +1921,9 @@
     <t>South Korea</t>
   </si>
   <si>
+    <t>South Sudan</t>
+  </si>
+  <si>
     <t>Southern Ocean</t>
   </si>
   <si>
@@ -1921,6 +1936,9 @@
     <t>Sri Lanka</t>
   </si>
   <si>
+    <t>State of Palestine</t>
+  </si>
+  <si>
     <t>Sudan</t>
   </si>
   <si>
@@ -1930,9 +1948,6 @@
     <t>Svalbard</t>
   </si>
   <si>
-    <t>Swaziland</t>
-  </si>
-  <si>
     <t>Sweden</t>
   </si>
   <si>
@@ -1957,6 +1972,9 @@
     <t>Thailand</t>
   </si>
   <si>
+    <t>Timor-Leste</t>
+  </si>
+  <si>
     <t>Togo</t>
   </si>
   <si>
@@ -2017,12 +2035,12 @@
     <t>Viet Nam</t>
   </si>
   <si>
+    <t>Wake Island</t>
+  </si>
+  <si>
     <t>Virgin Islands</t>
   </si>
   <si>
-    <t>Wake Island</t>
-  </si>
-  <si>
     <t>Wallis and Futuna</t>
   </si>
   <si>
@@ -2080,31 +2098,31 @@
     <t>restricted access</t>
   </si>
   <si>
-    <t>geographic location (country and/or sea)</t>
+    <t>geographic_location_country_andor_sea</t>
   </si>
   <si>
     <t>(Mandatory) The geographical origin of where the sample was collected from, with the intention of sequencing, as defined by the country or sea name. country or sea names should be chosen from the insdc country list (http://insdc.org/country.html).</t>
   </si>
   <si>
-    <t>gynecological disorder</t>
+    <t>gynecological_disorder</t>
   </si>
   <si>
     <t>(Optional) History of gynecological disorders; can include multiple disorders. the terms should be chosen from the do (human disease ontology) at http://www.disease-ontology.org, female reproductive system disease (https://disease-ontology.org/?id=doid:229).</t>
   </si>
   <si>
-    <t>urogenital disorder</t>
+    <t>urogenital_disorder</t>
   </si>
   <si>
     <t>(Optional) History of urogenital disorders, can include multiple disorders. the terms should be chosen from the do (human disease ontology) at http://www.disease-ontology.org, reproductive system disease (https://disease-ontology.org/?id=doid:15) or urinary system disease (https://disease-ontology.org/?id=doid:18).</t>
   </si>
   <si>
-    <t>host disease status</t>
+    <t>host_disease_status</t>
   </si>
   <si>
     <t>(Optional) List of diseases with which the host has been diagnosed; can include multiple diagnoses. the value of the field depends on host; for humans the terms should be chosen from do (disease ontology) at http://www.disease-ontology.org, other hosts are free text</t>
   </si>
   <si>
-    <t>host subject id</t>
+    <t>host_subject_id</t>
   </si>
   <si>
     <t>(Optional) A unique identifier by which each subject can be referred to, de-identified, e.g. #131</t>
@@ -2176,31 +2194,31 @@
     <t>99=99=Other</t>
   </si>
   <si>
-    <t>IHMC medication code</t>
+    <t>ihmc_medication_code</t>
   </si>
   <si>
     <t>(Optional) Can include multiple medication codes</t>
   </si>
   <si>
-    <t>host age</t>
+    <t>host_age</t>
   </si>
   <si>
     <t>(Optional) Age of host at the time of sampling; relevant scale depends on species and study, e.g. could be seconds for amoebae or centuries for trees (Units: years)</t>
   </si>
   <si>
-    <t>host body site</t>
+    <t>host_body_site</t>
   </si>
   <si>
     <t>(Optional) Name of body site where the sample was obtained from, such as a specific organ or tissue (tongue, lung etc...). for foundational model of anatomy ontology (fma) (v 3.1) terms, please see http://purl.bioontology.org/ontology/fma</t>
   </si>
   <si>
-    <t>host height</t>
-  </si>
-  <si>
-    <t>(Optional) The height of subject (Units: mm)</t>
-  </si>
-  <si>
-    <t>host body-mass index</t>
+    <t>host_height</t>
+  </si>
+  <si>
+    <t>(Optional) The height of subject (Units: m)</t>
+  </si>
+  <si>
+    <t>host_bodymass_index</t>
   </si>
   <si>
     <t>(Optional) Body mass index, calculated as weight/(height)squared (Units: kg/m2)</t>
@@ -2356,25 +2374,25 @@
     <t>99=99 Unknown/Refused</t>
   </si>
   <si>
-    <t>host occupation</t>
+    <t>host_occupation</t>
   </si>
   <si>
     <t>(Optional) Most frequent job performed by subject</t>
   </si>
   <si>
-    <t>host total mass</t>
+    <t>host_total_mass</t>
   </si>
   <si>
     <t>(Optional) Total mass of the host at collection, the unit depends on host (Units: kg)</t>
   </si>
   <si>
-    <t>host phenotype</t>
+    <t>host_phenotype</t>
   </si>
   <si>
     <t>(Optional) Phenotype of host. for phenotypic quality ontology (pato) (v 2013-10-28) terms, please see http://purl.bioontology.org/ontology/pato</t>
   </si>
   <si>
-    <t>host body temperature</t>
+    <t>host_body_temperature</t>
   </si>
   <si>
     <t>(Optional) Core body temperature of the host when sample was collected (Units: ºC)</t>
@@ -2392,13 +2410,13 @@
     <t>neuter</t>
   </si>
   <si>
-    <t>host sex</t>
+    <t>host_sex</t>
   </si>
   <si>
     <t>(Optional) Gender or sex of the host.</t>
   </si>
   <si>
-    <t>host scientific name</t>
+    <t>host_scientific_name</t>
   </si>
   <si>
     <t>(Optional) Scientific name of the natural (as opposed to laboratory) host to the organism from which sample was obtained.</t>
@@ -2410,7 +2428,7 @@
     <t>(Optional) Temperature of the sample at time of sampling (Units: ºC)</t>
   </si>
   <si>
-    <t>sample salinity</t>
+    <t>sample_salinity</t>
   </si>
   <si>
     <t>(Optional) Salinity is the total concentration of all dissolved salts in a liquid or solid (in the form of an extract obtained by centrifugation) sample. while salinity can be measured by a complete chemical analysis, this method is difficult and time consuming. more often, it is instead derived from the conductivity measurement. this is known as practical salinity. these derivations compare the specific conductance of the sample to a salinity standard such as seawater (Units: psu)</t>
@@ -2422,7 +2440,7 @@
     <t>(Optional) The total concentration of all dissolved salts in a liquid or solid sample. while salinity can be measured by a complete chemical analysis, this method is difficult and time consuming. more often, it is instead derived from the conductivity measurement. this is known as practical salinity. these derivations compare the specific conductance of the sample to a salinity standard such as seawater. (Units: psu)</t>
   </si>
   <si>
-    <t>source material identifiers</t>
+    <t>source_material_identifiers</t>
   </si>
   <si>
     <t>(Optional) A unique identifier assigned to a material sample (as defined by http://rs.tdwg.org/dwc/terms/materialsampleid, and as opposed to a particular digital record of a material sample) used for extracting nucleic acids, and subsequent sequencing. the identifier can refer either to the original material collected or to any derived sub-samples. the insdc qualifiers /specimen_voucher, /bio_material, or /culture_collection may or may not share the same value as the source_mat_id field. for instance, the /specimen_voucher qualifier and source_mat_id may both contain 'uam:herps:14' , referring to both the specimen voucher and sampled tissue with the same identifier. however, the /culture_collection qualifier may refer to a value from an initial culture (e.g. atcc:11775) while source_mat_id would refer to an identifier from some derived culture from which the nucleic acids were extracted (e.g. xatc123 or ark:/2154/r2).</t>
@@ -2434,7 +2452,7 @@
     <t>(Optional) Date of most recent menstruation</t>
   </si>
   <si>
-    <t>sexual activity</t>
+    <t>sexual_activity</t>
   </si>
   <si>
     <t>(Optional) Current sexual partner and frequency of sex</t>
@@ -2452,7 +2470,7 @@
     <t>(Optional) Date of most recent douche</t>
   </si>
   <si>
-    <t>birth control</t>
+    <t>birth_control</t>
   </si>
   <si>
     <t>(Optional) Specification of birth control medication used</t>
@@ -2464,7 +2482,7 @@
     <t>(Optional) Date of onset of menopause</t>
   </si>
   <si>
-    <t>HRT</t>
+    <t>hrt</t>
   </si>
   <si>
     <t>(Optional) Whether subject had hormone replacement theraphy, and if yes start date</t>
@@ -2476,37 +2494,37 @@
     <t>(Optional) Specification of whether hysterectomy was performed</t>
   </si>
   <si>
-    <t>host diet</t>
+    <t>host_diet</t>
   </si>
   <si>
     <t>(Optional) Type of diet depending on the host, for animals omnivore, herbivore etc., for humans high-fat, mediterranean etc.; can include multiple diet types</t>
   </si>
   <si>
-    <t>host last meal</t>
+    <t>host_last_meal</t>
   </si>
   <si>
     <t>(Optional) Content of last meal and time since feeding; can include multiple values</t>
   </si>
   <si>
-    <t>host family relationship</t>
+    <t>host_family_relationship</t>
   </si>
   <si>
     <t>(Optional) Familial relationships to other hosts in the same study; can include multiple relationships</t>
   </si>
   <si>
-    <t>host genotype</t>
+    <t>host_genotype</t>
   </si>
   <si>
     <t>(Optional) Observed genotype</t>
   </si>
   <si>
-    <t>host pulse</t>
+    <t>host_pulse</t>
   </si>
   <si>
     <t>(Optional) Resting pulse, measured as beats per minute (Units: bpm)</t>
   </si>
   <si>
-    <t>host body product</t>
+    <t>host_body_product</t>
   </si>
   <si>
     <t>(Optional) Substance produced by the body, e.g. stool, mucus, where the sample was obtained from. for foundational model of anatomy ontology (fma) (v 3.1) terms, please see http://purl.bioontology.org/ontology/fma</t>
@@ -2518,121 +2536,121 @@
     <t>(Optional) Type of perturbation, e.g. chemical administration, physical disturbance, etc., coupled with time that perturbation occurred; can include multiple perturbation types</t>
   </si>
   <si>
-    <t>negative control type</t>
+    <t>negative_control_type</t>
   </si>
   <si>
     <t>(Optional) The substance or equipment used as a negative control in an investigation</t>
   </si>
   <si>
-    <t>positive control type</t>
+    <t>positive_control_type</t>
   </si>
   <si>
     <t>(Optional) The substance, mixture, product, or apparatus used to verify that a process which is part of an investigation delivers a true positive.</t>
   </si>
   <si>
-    <t>experimental factor</t>
+    <t>experimental_factor</t>
   </si>
   <si>
     <t>(Optional) Experimental factors are essentially the variable aspects of an experiment design which can be used to describe an experiment, or set of experiments, in an increasingly detailed manner. this field accepts ontology terms from experimental factor ontology (efo) and/or ontology for biomedical investigations (obi). for a browser of efo (v 2.95) terms, please see http://purl.bioontology.org/ontology/efo; for a browser of obi (v 2018-02-12) terms please see http://purl.bioontology.org/ontology/obi. e.g. time series design [efo:efo_0001779]</t>
   </si>
   <si>
-    <t>encoded traits</t>
+    <t>encoded_traits</t>
   </si>
   <si>
     <t>(Optional) Should include key traits like antibiotic resistance or xenobiotic degradation phenotypes for plasmids, converting genes for phage</t>
   </si>
   <si>
-    <t>subspecific genetic lineage</t>
+    <t>subspecific_genetic_lineage</t>
   </si>
   <si>
     <t>(Optional) Information about the genetic distinctness of the sequenced organism below the subspecies level, e.g., serovar, serotype, biotype, ecotype, or any relevant genetic typing schemes like group i plasmid. subspecies should not be recorded in this term, but in the ncbi taxonomy. supply both the lineage name and the lineage rank separated by a colon, e.g., biovar:abc123.</t>
   </si>
   <si>
-    <t>taxonomic classification</t>
+    <t>taxonomic_classification</t>
   </si>
   <si>
     <t>(Optional) Method used for taxonomic classification, along with reference database used, classification rank, and thresholds used to classify new genomes. expected values are: classification method, database name, and other parameters e.g. vcontact vcontact2 (references from ncbi refseq v83, genus rank classification, default parameters)</t>
   </si>
   <si>
-    <t>isolation and growth condition</t>
+    <t>isolation_and_growth_condition</t>
   </si>
   <si>
     <t>(Optional) Publication reference in the form of pubmed id (pmid), digital object identifier (doi) or url for isolation and growth condition specifications of the organism/material. mandatory for migs and mimarks specimen.</t>
   </si>
   <si>
-    <t>annotation source</t>
+    <t>annotation_source</t>
   </si>
   <si>
     <t>(Optional) For cases where annotation was provided by a community jamboree or model organism database rather than by a specific submitter</t>
   </si>
   <si>
-    <t>reference for biomaterial</t>
+    <t>reference_for_biomaterial</t>
   </si>
   <si>
     <t>(Optional) Primary publication if isolated before genome publication; otherwise, primary genome report. mandatory for migs of bacteria and archaea.</t>
   </si>
   <si>
-    <t>sample material processing</t>
+    <t>sample_material_processing</t>
   </si>
   <si>
     <t>(Optional) A brief description of any processing applied to the sample during or after retrieving the sample from environment, or a link to the relevant protocol(s) performed.</t>
   </si>
   <si>
-    <t>sample volume or weight for DNA extraction</t>
-  </si>
-  <si>
-    <t>(Optional) Volume (ml) or mass (g) of total collected sample processed for dna extraction. note: total sample collected should be entered under the term 'sample size'. (Units: ng)</t>
-  </si>
-  <si>
-    <t>nucleic acid extraction</t>
+    <t>sample_volume_or_weight_for_dna_extraction</t>
+  </si>
+  <si>
+    <t>(Optional) Volume (ml) or mass (g) of total collected sample processed for dna extraction. note: total sample collected should be entered under the term 'sample size'. (Units: mL)</t>
+  </si>
+  <si>
+    <t>nucleic_acid_extraction</t>
   </si>
   <si>
     <t>(Optional) A link to a literature reference, electronic resource or a standard operating procedure (sop), that describes the material separation to recover the nucleic acid fraction from a sample</t>
   </si>
   <si>
-    <t>nucleic acid amplification</t>
+    <t>nucleic_acid_amplification</t>
   </si>
   <si>
     <t>(Optional) A link to a literature reference, electronic resource or a standard operating procedure (sop), that describes the enzymatic amplification (pcr, tma, nasba) of specific nucleic acids</t>
   </si>
   <si>
-    <t>library size</t>
+    <t>library_size</t>
   </si>
   <si>
     <t>(Optional) Total number of clones in the library prepared for the project</t>
   </si>
   <si>
-    <t>library reads sequenced</t>
+    <t>library_reads_sequenced</t>
   </si>
   <si>
     <t>(Optional) Total number of clones sequenced from the library</t>
   </si>
   <si>
-    <t>library construction method</t>
+    <t>library_construction_method</t>
   </si>
   <si>
     <t>(Optional) Library construction method used for clone libraries</t>
   </si>
   <si>
-    <t>library vector</t>
+    <t>library_vector</t>
   </si>
   <si>
     <t>(Optional) Cloning vector type(s) used in construction of libraries</t>
   </si>
   <si>
-    <t>library screening strategy</t>
+    <t>library_screening_strategy</t>
   </si>
   <si>
     <t>(Optional) Specific enrichment or screening methods applied before and/or after creating clone libraries in order to select a specific group of sequences</t>
   </si>
   <si>
-    <t>pcr conditions</t>
+    <t>pcr_conditions</t>
   </si>
   <si>
     <t>(Optional) Description of reaction conditions and components for pcr in the form of 'initial denaturation:94degc_1.5min; annealing=...'</t>
   </si>
   <si>
-    <t>pcr primers</t>
+    <t>pcr_primers</t>
   </si>
   <si>
     <t>(Optional) Pcr primers that were used to amplify the sequence of the targeted gene, locus or subfragment. this field should contain all the primers used for a single pcr reaction if multiple forward or reverse primers are present in a single pcr reaction. the primer sequence should be reported in uppercase letters</t>
@@ -2644,7 +2662,7 @@
     <t>(Optional) Adapters provide priming sequences for both amplification and sequencing of the sample-library fragments. both adapters should be reported; in uppercase letters</t>
   </si>
   <si>
-    <t>chemical administration</t>
+    <t>chemical_administration</t>
   </si>
   <si>
     <t>(Optional) List of chemical compounds administered to the host or site where sampling occurred, and when (e.g. antibiotics, n fertilizer, air filter); can include multiple compounds. for chemical entities of biological interest ontology (chebi) (v111), please see http://purl.bioontology.org/ontology/chebi</t>
@@ -3177,7 +3195,7 @@
         <v>143</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -3221,7 +3239,7 @@
         <v>144</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
   </sheetData>
@@ -3248,7 +3266,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N86"/>
+  <dimension ref="G1:N87"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -3972,6 +3990,11 @@
     </row>
     <row r="86" spans="14:14">
       <c r="N86" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="87" spans="14:14">
+      <c r="N87" t="s">
         <v>117</v>
       </c>
     </row>
@@ -3993,27 +4016,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -4033,122 +4056,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
   </sheetData>
@@ -4172,588 +4195,588 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>679</v>
+        <v>685</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>683</v>
+        <v>689</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>687</v>
+        <v>693</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>711</v>
+        <v>717</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>713</v>
+        <v>719</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>715</v>
+        <v>721</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>717</v>
+        <v>723</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>719</v>
+        <v>725</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>721</v>
+        <v>727</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>771</v>
+        <v>777</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>773</v>
+        <v>779</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>775</v>
+        <v>781</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>777</v>
+        <v>783</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>783</v>
+        <v>789</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>785</v>
+        <v>791</v>
       </c>
       <c r="BF1" s="1" t="s">
-        <v>787</v>
+        <v>793</v>
       </c>
       <c r="BG1" s="1" t="s">
-        <v>789</v>
+        <v>795</v>
       </c>
       <c r="BH1" s="1" t="s">
-        <v>791</v>
+        <v>797</v>
       </c>
       <c r="BI1" s="1" t="s">
-        <v>793</v>
+        <v>799</v>
       </c>
       <c r="BJ1" s="1" t="s">
-        <v>795</v>
+        <v>801</v>
       </c>
       <c r="BK1" s="1" t="s">
-        <v>797</v>
+        <v>803</v>
       </c>
       <c r="BL1" s="1" t="s">
-        <v>799</v>
+        <v>805</v>
       </c>
       <c r="BM1" s="1" t="s">
-        <v>801</v>
+        <v>807</v>
       </c>
       <c r="BN1" s="1" t="s">
-        <v>803</v>
+        <v>809</v>
       </c>
       <c r="BO1" s="1" t="s">
-        <v>805</v>
+        <v>811</v>
       </c>
       <c r="BP1" s="1" t="s">
-        <v>807</v>
+        <v>813</v>
       </c>
       <c r="BQ1" s="1" t="s">
-        <v>809</v>
+        <v>815</v>
       </c>
       <c r="BR1" s="1" t="s">
-        <v>811</v>
+        <v>817</v>
       </c>
       <c r="BS1" s="1" t="s">
-        <v>813</v>
+        <v>819</v>
       </c>
       <c r="BT1" s="1" t="s">
-        <v>815</v>
+        <v>821</v>
       </c>
       <c r="BU1" s="1" t="s">
-        <v>817</v>
+        <v>823</v>
       </c>
       <c r="BV1" s="1" t="s">
-        <v>819</v>
+        <v>825</v>
       </c>
       <c r="BW1" s="1" t="s">
-        <v>821</v>
+        <v>827</v>
       </c>
       <c r="BX1" s="1" t="s">
-        <v>823</v>
+        <v>829</v>
       </c>
       <c r="BY1" s="1" t="s">
-        <v>825</v>
+        <v>831</v>
       </c>
       <c r="BZ1" s="1" t="s">
-        <v>827</v>
+        <v>833</v>
       </c>
       <c r="CA1" s="1" t="s">
-        <v>829</v>
+        <v>835</v>
       </c>
       <c r="CB1" s="1" t="s">
-        <v>831</v>
+        <v>837</v>
       </c>
       <c r="CC1" s="1" t="s">
-        <v>833</v>
+        <v>839</v>
       </c>
       <c r="CD1" s="1" t="s">
-        <v>835</v>
+        <v>841</v>
       </c>
       <c r="CE1" s="1" t="s">
-        <v>837</v>
+        <v>843</v>
       </c>
       <c r="CF1" s="1" t="s">
-        <v>839</v>
+        <v>845</v>
       </c>
       <c r="CG1" s="1" t="s">
-        <v>841</v>
+        <v>847</v>
       </c>
       <c r="CH1" s="1" t="s">
-        <v>843</v>
+        <v>849</v>
       </c>
       <c r="CI1" s="1" t="s">
-        <v>845</v>
+        <v>851</v>
       </c>
       <c r="CJ1" s="1" t="s">
-        <v>847</v>
+        <v>853</v>
       </c>
       <c r="CK1" s="1" t="s">
-        <v>849</v>
+        <v>855</v>
       </c>
       <c r="CL1" s="1" t="s">
-        <v>851</v>
+        <v>857</v>
       </c>
       <c r="CM1" s="1" t="s">
-        <v>853</v>
+        <v>859</v>
       </c>
       <c r="CN1" s="1" t="s">
-        <v>855</v>
+        <v>861</v>
       </c>
       <c r="CO1" s="1" t="s">
-        <v>857</v>
+        <v>863</v>
       </c>
       <c r="CP1" s="1" t="s">
-        <v>859</v>
+        <v>865</v>
       </c>
       <c r="CQ1" s="1" t="s">
-        <v>861</v>
+        <v>867</v>
       </c>
       <c r="CR1" s="1" t="s">
-        <v>863</v>
+        <v>869</v>
       </c>
       <c r="CS1" s="1" t="s">
-        <v>865</v>
+        <v>871</v>
       </c>
       <c r="CT1" s="1" t="s">
-        <v>867</v>
+        <v>873</v>
       </c>
     </row>
     <row r="2" spans="1:98" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AJ2" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AK2" s="2" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AL2" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AM2" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AN2" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AO2" s="2" t="s">
-        <v>680</v>
+        <v>686</v>
       </c>
       <c r="AP2" s="2" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="AQ2" s="2" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="AR2" s="2" t="s">
-        <v>686</v>
+        <v>692</v>
       </c>
       <c r="AS2" s="2" t="s">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="AT2" s="2" t="s">
-        <v>712</v>
+        <v>718</v>
       </c>
       <c r="AU2" s="2" t="s">
-        <v>714</v>
+        <v>720</v>
       </c>
       <c r="AV2" s="2" t="s">
-        <v>716</v>
+        <v>722</v>
       </c>
       <c r="AW2" s="2" t="s">
-        <v>718</v>
+        <v>724</v>
       </c>
       <c r="AX2" s="2" t="s">
-        <v>720</v>
+        <v>726</v>
       </c>
       <c r="AY2" s="2" t="s">
-        <v>722</v>
+        <v>728</v>
       </c>
       <c r="AZ2" s="2" t="s">
-        <v>772</v>
+        <v>778</v>
       </c>
       <c r="BA2" s="2" t="s">
-        <v>774</v>
+        <v>780</v>
       </c>
       <c r="BB2" s="2" t="s">
-        <v>776</v>
+        <v>782</v>
       </c>
       <c r="BC2" s="2" t="s">
-        <v>778</v>
+        <v>784</v>
       </c>
       <c r="BD2" s="2" t="s">
-        <v>784</v>
+        <v>790</v>
       </c>
       <c r="BE2" s="2" t="s">
-        <v>786</v>
+        <v>792</v>
       </c>
       <c r="BF2" s="2" t="s">
-        <v>788</v>
+        <v>794</v>
       </c>
       <c r="BG2" s="2" t="s">
-        <v>790</v>
+        <v>796</v>
       </c>
       <c r="BH2" s="2" t="s">
-        <v>792</v>
+        <v>798</v>
       </c>
       <c r="BI2" s="2" t="s">
-        <v>794</v>
+        <v>800</v>
       </c>
       <c r="BJ2" s="2" t="s">
-        <v>796</v>
+        <v>802</v>
       </c>
       <c r="BK2" s="2" t="s">
-        <v>798</v>
+        <v>804</v>
       </c>
       <c r="BL2" s="2" t="s">
-        <v>800</v>
+        <v>806</v>
       </c>
       <c r="BM2" s="2" t="s">
-        <v>802</v>
+        <v>808</v>
       </c>
       <c r="BN2" s="2" t="s">
-        <v>804</v>
+        <v>810</v>
       </c>
       <c r="BO2" s="2" t="s">
-        <v>806</v>
+        <v>812</v>
       </c>
       <c r="BP2" s="2" t="s">
-        <v>808</v>
+        <v>814</v>
       </c>
       <c r="BQ2" s="2" t="s">
-        <v>810</v>
+        <v>816</v>
       </c>
       <c r="BR2" s="2" t="s">
-        <v>812</v>
+        <v>818</v>
       </c>
       <c r="BS2" s="2" t="s">
-        <v>814</v>
+        <v>820</v>
       </c>
       <c r="BT2" s="2" t="s">
-        <v>816</v>
+        <v>822</v>
       </c>
       <c r="BU2" s="2" t="s">
-        <v>818</v>
+        <v>824</v>
       </c>
       <c r="BV2" s="2" t="s">
-        <v>820</v>
+        <v>826</v>
       </c>
       <c r="BW2" s="2" t="s">
-        <v>822</v>
+        <v>828</v>
       </c>
       <c r="BX2" s="2" t="s">
-        <v>824</v>
+        <v>830</v>
       </c>
       <c r="BY2" s="2" t="s">
-        <v>826</v>
+        <v>832</v>
       </c>
       <c r="BZ2" s="2" t="s">
-        <v>828</v>
+        <v>834</v>
       </c>
       <c r="CA2" s="2" t="s">
-        <v>830</v>
+        <v>836</v>
       </c>
       <c r="CB2" s="2" t="s">
-        <v>832</v>
+        <v>838</v>
       </c>
       <c r="CC2" s="2" t="s">
-        <v>834</v>
+        <v>840</v>
       </c>
       <c r="CD2" s="2" t="s">
-        <v>836</v>
+        <v>842</v>
       </c>
       <c r="CE2" s="2" t="s">
-        <v>838</v>
+        <v>844</v>
       </c>
       <c r="CF2" s="2" t="s">
-        <v>840</v>
+        <v>846</v>
       </c>
       <c r="CG2" s="2" t="s">
-        <v>842</v>
+        <v>848</v>
       </c>
       <c r="CH2" s="2" t="s">
-        <v>844</v>
+        <v>850</v>
       </c>
       <c r="CI2" s="2" t="s">
-        <v>846</v>
+        <v>852</v>
       </c>
       <c r="CJ2" s="2" t="s">
-        <v>848</v>
+        <v>854</v>
       </c>
       <c r="CK2" s="2" t="s">
-        <v>850</v>
+        <v>856</v>
       </c>
       <c r="CL2" s="2" t="s">
-        <v>852</v>
+        <v>858</v>
       </c>
       <c r="CM2" s="2" t="s">
-        <v>854</v>
+        <v>860</v>
       </c>
       <c r="CN2" s="2" t="s">
-        <v>856</v>
+        <v>862</v>
       </c>
       <c r="CO2" s="2" t="s">
-        <v>858</v>
+        <v>864</v>
       </c>
       <c r="CP2" s="2" t="s">
-        <v>860</v>
+        <v>866</v>
       </c>
       <c r="CQ2" s="2" t="s">
-        <v>862</v>
+        <v>868</v>
       </c>
       <c r="CR2" s="2" t="s">
-        <v>864</v>
+        <v>870</v>
       </c>
       <c r="CS2" s="2" t="s">
-        <v>866</v>
+        <v>872</v>
       </c>
       <c r="CT2" s="2" t="s">
-        <v>868</v>
+        <v>874</v>
       </c>
     </row>
   </sheetData>
@@ -4780,7 +4803,7 @@
       <formula1>geographiclocationcountryandorsea</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AT3:AT101">
-      <formula1>IHMCmedicationcode</formula1>
+      <formula1>ihmcmedicationcode</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AZ3:AZ101">
       <formula1>hostoccupation</formula1>
@@ -4798,339 +4821,339 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="E1:BQ289"/>
+  <dimension ref="E1:BQ294"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="5:69">
       <c r="E1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="O1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="P1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Y1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AO1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AT1" t="s">
-        <v>689</v>
+        <v>695</v>
       </c>
       <c r="AZ1" t="s">
-        <v>723</v>
+        <v>729</v>
       </c>
       <c r="BD1" t="s">
-        <v>779</v>
+        <v>785</v>
       </c>
       <c r="BQ1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="2" spans="5:69">
       <c r="E2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="P2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Y2" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AO2" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AT2" t="s">
-        <v>690</v>
+        <v>696</v>
       </c>
       <c r="AZ2" t="s">
-        <v>724</v>
+        <v>730</v>
       </c>
       <c r="BD2" t="s">
-        <v>780</v>
+        <v>786</v>
       </c>
       <c r="BQ2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="3" spans="5:69">
       <c r="E3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Y3" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AO3" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AT3" t="s">
-        <v>691</v>
+        <v>697</v>
       </c>
       <c r="AZ3" t="s">
-        <v>725</v>
+        <v>731</v>
       </c>
       <c r="BD3" t="s">
-        <v>781</v>
+        <v>787</v>
       </c>
     </row>
     <row r="4" spans="5:69">
       <c r="E4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AO4" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AT4" t="s">
-        <v>692</v>
+        <v>698</v>
       </c>
       <c r="AZ4" t="s">
-        <v>726</v>
+        <v>732</v>
       </c>
       <c r="BD4" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
     </row>
     <row r="5" spans="5:69">
       <c r="E5" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F5" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H5" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AO5" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AT5" t="s">
-        <v>693</v>
+        <v>699</v>
       </c>
       <c r="AZ5" t="s">
-        <v>727</v>
+        <v>733</v>
       </c>
       <c r="BD5" t="s">
-        <v>668</v>
+        <v>674</v>
       </c>
     </row>
     <row r="6" spans="5:69">
       <c r="E6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AO6" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AT6" t="s">
-        <v>694</v>
+        <v>700</v>
       </c>
       <c r="AZ6" t="s">
-        <v>728</v>
+        <v>734</v>
       </c>
       <c r="BD6" t="s">
-        <v>669</v>
+        <v>675</v>
       </c>
     </row>
     <row r="7" spans="5:69">
       <c r="E7" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H7" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AO7" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AT7" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="AZ7" t="s">
-        <v>729</v>
+        <v>735</v>
       </c>
       <c r="BD7" t="s">
-        <v>670</v>
+        <v>676</v>
       </c>
     </row>
     <row r="8" spans="5:69">
       <c r="E8" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AO8" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AT8" t="s">
-        <v>696</v>
+        <v>702</v>
       </c>
       <c r="AZ8" t="s">
-        <v>730</v>
+        <v>736</v>
       </c>
       <c r="BD8" t="s">
-        <v>671</v>
+        <v>677</v>
       </c>
     </row>
     <row r="9" spans="5:69">
       <c r="E9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AO9" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AT9" t="s">
-        <v>697</v>
+        <v>703</v>
       </c>
       <c r="AZ9" t="s">
-        <v>731</v>
+        <v>737</v>
       </c>
       <c r="BD9" t="s">
-        <v>672</v>
+        <v>678</v>
       </c>
     </row>
     <row r="10" spans="5:69">
       <c r="E10" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AO10" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AT10" t="s">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="AZ10" t="s">
-        <v>732</v>
+        <v>738</v>
       </c>
       <c r="BD10" t="s">
-        <v>673</v>
+        <v>679</v>
       </c>
     </row>
     <row r="11" spans="5:69">
       <c r="E11" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AO11" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AT11" t="s">
-        <v>699</v>
+        <v>705</v>
       </c>
       <c r="AZ11" t="s">
-        <v>733</v>
+        <v>739</v>
       </c>
       <c r="BD11" t="s">
-        <v>674</v>
+        <v>680</v>
       </c>
     </row>
     <row r="12" spans="5:69">
       <c r="E12" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AO12" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AT12" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="AZ12" t="s">
-        <v>734</v>
+        <v>740</v>
       </c>
       <c r="BD12" t="s">
-        <v>782</v>
+        <v>788</v>
       </c>
     </row>
     <row r="13" spans="5:69">
       <c r="E13" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AO13" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AT13" t="s">
-        <v>701</v>
+        <v>707</v>
       </c>
       <c r="AZ13" t="s">
-        <v>735</v>
+        <v>741</v>
       </c>
       <c r="BD13" t="s">
-        <v>675</v>
+        <v>681</v>
       </c>
     </row>
     <row r="14" spans="5:69">
       <c r="E14" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AO14" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AT14" t="s">
-        <v>702</v>
+        <v>708</v>
       </c>
       <c r="AZ14" t="s">
-        <v>736</v>
+        <v>742</v>
       </c>
       <c r="BD14" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
     </row>
     <row r="15" spans="5:69">
       <c r="E15" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AO15" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AT15" t="s">
-        <v>703</v>
+        <v>709</v>
       </c>
       <c r="AZ15" t="s">
-        <v>737</v>
+        <v>743</v>
       </c>
       <c r="BD15" t="s">
-        <v>677</v>
+        <v>683</v>
       </c>
     </row>
     <row r="16" spans="5:69">
       <c r="E16" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AO16" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AT16" t="s">
-        <v>704</v>
+        <v>710</v>
       </c>
       <c r="AZ16" t="s">
-        <v>738</v>
+        <v>744</v>
       </c>
       <c r="BD16" t="s">
         <v>116</v>
@@ -5138,1526 +5161,1551 @@
     </row>
     <row r="17" spans="5:56">
       <c r="E17" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AO17" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AT17" t="s">
-        <v>705</v>
+        <v>711</v>
       </c>
       <c r="AZ17" t="s">
-        <v>739</v>
+        <v>745</v>
       </c>
       <c r="BD17" t="s">
-        <v>678</v>
+        <v>684</v>
       </c>
     </row>
     <row r="18" spans="5:56">
       <c r="E18" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AO18" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AT18" t="s">
-        <v>706</v>
+        <v>712</v>
       </c>
       <c r="AZ18" t="s">
-        <v>740</v>
+        <v>746</v>
       </c>
     </row>
     <row r="19" spans="5:56">
       <c r="E19" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AO19" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AT19" t="s">
-        <v>707</v>
+        <v>713</v>
       </c>
       <c r="AZ19" t="s">
-        <v>741</v>
+        <v>747</v>
       </c>
     </row>
     <row r="20" spans="5:56">
       <c r="E20" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AO20" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AT20" t="s">
-        <v>708</v>
+        <v>714</v>
       </c>
       <c r="AZ20" t="s">
-        <v>742</v>
+        <v>748</v>
       </c>
     </row>
     <row r="21" spans="5:56">
       <c r="E21" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AO21" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AT21" t="s">
-        <v>709</v>
+        <v>715</v>
       </c>
       <c r="AZ21" t="s">
-        <v>743</v>
+        <v>749</v>
       </c>
     </row>
     <row r="22" spans="5:56">
       <c r="E22" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AO22" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AT22" t="s">
-        <v>710</v>
+        <v>716</v>
       </c>
       <c r="AZ22" t="s">
-        <v>744</v>
+        <v>750</v>
       </c>
     </row>
     <row r="23" spans="5:56">
       <c r="E23" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AO23" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AZ23" t="s">
-        <v>745</v>
+        <v>751</v>
       </c>
     </row>
     <row r="24" spans="5:56">
       <c r="E24" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AO24" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AZ24" t="s">
-        <v>746</v>
+        <v>752</v>
       </c>
     </row>
     <row r="25" spans="5:56">
       <c r="E25" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AO25" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AZ25" t="s">
-        <v>747</v>
+        <v>753</v>
       </c>
     </row>
     <row r="26" spans="5:56">
       <c r="E26" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AO26" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AZ26" t="s">
-        <v>748</v>
+        <v>754</v>
       </c>
     </row>
     <row r="27" spans="5:56">
       <c r="E27" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AO27" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AZ27" t="s">
-        <v>749</v>
+        <v>755</v>
       </c>
     </row>
     <row r="28" spans="5:56">
       <c r="E28" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AO28" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AZ28" t="s">
-        <v>750</v>
+        <v>756</v>
       </c>
     </row>
     <row r="29" spans="5:56">
       <c r="E29" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AO29" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AZ29" t="s">
-        <v>751</v>
+        <v>757</v>
       </c>
     </row>
     <row r="30" spans="5:56">
       <c r="E30" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AO30" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AZ30" t="s">
-        <v>752</v>
+        <v>758</v>
       </c>
     </row>
     <row r="31" spans="5:56">
       <c r="AO31" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AZ31" t="s">
-        <v>753</v>
+        <v>759</v>
       </c>
     </row>
     <row r="32" spans="5:56">
       <c r="AO32" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AZ32" t="s">
-        <v>754</v>
+        <v>760</v>
       </c>
     </row>
     <row r="33" spans="41:52">
       <c r="AO33" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AZ33" t="s">
-        <v>755</v>
+        <v>761</v>
       </c>
     </row>
     <row r="34" spans="41:52">
       <c r="AO34" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AZ34" t="s">
-        <v>756</v>
+        <v>762</v>
       </c>
     </row>
     <row r="35" spans="41:52">
       <c r="AO35" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AZ35" t="s">
-        <v>757</v>
+        <v>763</v>
       </c>
     </row>
     <row r="36" spans="41:52">
       <c r="AO36" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AZ36" t="s">
-        <v>758</v>
+        <v>764</v>
       </c>
     </row>
     <row r="37" spans="41:52">
       <c r="AO37" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AZ37" t="s">
-        <v>759</v>
+        <v>765</v>
       </c>
     </row>
     <row r="38" spans="41:52">
       <c r="AO38" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AZ38" t="s">
-        <v>760</v>
+        <v>766</v>
       </c>
     </row>
     <row r="39" spans="41:52">
       <c r="AO39" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AZ39" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
     </row>
     <row r="40" spans="41:52">
       <c r="AO40" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AZ40" t="s">
-        <v>762</v>
+        <v>768</v>
       </c>
     </row>
     <row r="41" spans="41:52">
       <c r="AO41" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AZ41" t="s">
-        <v>763</v>
+        <v>769</v>
       </c>
     </row>
     <row r="42" spans="41:52">
       <c r="AO42" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AZ42" t="s">
-        <v>764</v>
+        <v>770</v>
       </c>
     </row>
     <row r="43" spans="41:52">
       <c r="AO43" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AZ43" t="s">
-        <v>765</v>
+        <v>771</v>
       </c>
     </row>
     <row r="44" spans="41:52">
       <c r="AO44" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AZ44" t="s">
-        <v>766</v>
+        <v>772</v>
       </c>
     </row>
     <row r="45" spans="41:52">
       <c r="AO45" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AZ45" t="s">
-        <v>767</v>
+        <v>773</v>
       </c>
     </row>
     <row r="46" spans="41:52">
       <c r="AO46" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AZ46" t="s">
-        <v>768</v>
+        <v>774</v>
       </c>
     </row>
     <row r="47" spans="41:52">
       <c r="AO47" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AZ47" t="s">
-        <v>769</v>
+        <v>775</v>
       </c>
     </row>
     <row r="48" spans="41:52">
       <c r="AO48" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AZ48" t="s">
-        <v>770</v>
+        <v>776</v>
       </c>
     </row>
     <row r="49" spans="41:41">
       <c r="AO49" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="50" spans="41:41">
       <c r="AO50" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="51" spans="41:41">
       <c r="AO51" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="52" spans="41:41">
       <c r="AO52" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="53" spans="41:41">
       <c r="AO53" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="54" spans="41:41">
       <c r="AO54" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="55" spans="41:41">
       <c r="AO55" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="56" spans="41:41">
       <c r="AO56" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="57" spans="41:41">
       <c r="AO57" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="58" spans="41:41">
       <c r="AO58" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="59" spans="41:41">
       <c r="AO59" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="60" spans="41:41">
       <c r="AO60" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="61" spans="41:41">
       <c r="AO61" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="62" spans="41:41">
       <c r="AO62" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="63" spans="41:41">
       <c r="AO63" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="64" spans="41:41">
       <c r="AO64" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="65" spans="41:41">
       <c r="AO65" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="66" spans="41:41">
       <c r="AO66" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="67" spans="41:41">
       <c r="AO67" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="68" spans="41:41">
       <c r="AO68" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="69" spans="41:41">
       <c r="AO69" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="70" spans="41:41">
       <c r="AO70" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="71" spans="41:41">
       <c r="AO71" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="72" spans="41:41">
       <c r="AO72" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="73" spans="41:41">
       <c r="AO73" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="74" spans="41:41">
       <c r="AO74" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="75" spans="41:41">
       <c r="AO75" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="76" spans="41:41">
       <c r="AO76" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="77" spans="41:41">
       <c r="AO77" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="78" spans="41:41">
       <c r="AO78" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="79" spans="41:41">
       <c r="AO79" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="80" spans="41:41">
       <c r="AO80" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="81" spans="41:41">
       <c r="AO81" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="82" spans="41:41">
       <c r="AO82" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="83" spans="41:41">
       <c r="AO83" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="84" spans="41:41">
       <c r="AO84" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="85" spans="41:41">
       <c r="AO85" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="86" spans="41:41">
       <c r="AO86" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="87" spans="41:41">
       <c r="AO87" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="88" spans="41:41">
       <c r="AO88" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="89" spans="41:41">
       <c r="AO89" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="90" spans="41:41">
       <c r="AO90" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="91" spans="41:41">
       <c r="AO91" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="92" spans="41:41">
       <c r="AO92" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="93" spans="41:41">
       <c r="AO93" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="94" spans="41:41">
       <c r="AO94" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="95" spans="41:41">
       <c r="AO95" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="96" spans="41:41">
       <c r="AO96" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="97" spans="41:41">
       <c r="AO97" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="98" spans="41:41">
       <c r="AO98" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="99" spans="41:41">
       <c r="AO99" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="100" spans="41:41">
       <c r="AO100" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="101" spans="41:41">
       <c r="AO101" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="102" spans="41:41">
       <c r="AO102" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="103" spans="41:41">
       <c r="AO103" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="104" spans="41:41">
       <c r="AO104" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="105" spans="41:41">
       <c r="AO105" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="106" spans="41:41">
       <c r="AO106" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="107" spans="41:41">
       <c r="AO107" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="108" spans="41:41">
       <c r="AO108" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="109" spans="41:41">
       <c r="AO109" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="110" spans="41:41">
       <c r="AO110" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="111" spans="41:41">
       <c r="AO111" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="112" spans="41:41">
       <c r="AO112" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="113" spans="41:41">
       <c r="AO113" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="114" spans="41:41">
       <c r="AO114" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="115" spans="41:41">
       <c r="AO115" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="116" spans="41:41">
       <c r="AO116" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="117" spans="41:41">
       <c r="AO117" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="118" spans="41:41">
       <c r="AO118" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="119" spans="41:41">
       <c r="AO119" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="120" spans="41:41">
       <c r="AO120" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="121" spans="41:41">
       <c r="AO121" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="122" spans="41:41">
       <c r="AO122" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="123" spans="41:41">
       <c r="AO123" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="124" spans="41:41">
       <c r="AO124" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="125" spans="41:41">
       <c r="AO125" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="126" spans="41:41">
       <c r="AO126" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="127" spans="41:41">
       <c r="AO127" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="128" spans="41:41">
       <c r="AO128" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="129" spans="41:41">
       <c r="AO129" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="130" spans="41:41">
       <c r="AO130" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="131" spans="41:41">
       <c r="AO131" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="132" spans="41:41">
       <c r="AO132" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="133" spans="41:41">
       <c r="AO133" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="134" spans="41:41">
       <c r="AO134" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="135" spans="41:41">
       <c r="AO135" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="136" spans="41:41">
       <c r="AO136" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="137" spans="41:41">
       <c r="AO137" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="138" spans="41:41">
       <c r="AO138" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="139" spans="41:41">
       <c r="AO139" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="140" spans="41:41">
       <c r="AO140" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="141" spans="41:41">
       <c r="AO141" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="142" spans="41:41">
       <c r="AO142" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="143" spans="41:41">
       <c r="AO143" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="144" spans="41:41">
       <c r="AO144" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="145" spans="41:41">
       <c r="AO145" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="146" spans="41:41">
       <c r="AO146" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="147" spans="41:41">
       <c r="AO147" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="148" spans="41:41">
       <c r="AO148" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="149" spans="41:41">
       <c r="AO149" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="150" spans="41:41">
       <c r="AO150" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="151" spans="41:41">
       <c r="AO151" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="152" spans="41:41">
       <c r="AO152" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="153" spans="41:41">
       <c r="AO153" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="154" spans="41:41">
       <c r="AO154" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="155" spans="41:41">
       <c r="AO155" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="156" spans="41:41">
       <c r="AO156" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="157" spans="41:41">
       <c r="AO157" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="158" spans="41:41">
       <c r="AO158" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="159" spans="41:41">
       <c r="AO159" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="160" spans="41:41">
       <c r="AO160" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="161" spans="41:41">
       <c r="AO161" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="162" spans="41:41">
       <c r="AO162" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="163" spans="41:41">
       <c r="AO163" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="164" spans="41:41">
       <c r="AO164" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="165" spans="41:41">
       <c r="AO165" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="166" spans="41:41">
       <c r="AO166" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="167" spans="41:41">
       <c r="AO167" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="168" spans="41:41">
       <c r="AO168" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="169" spans="41:41">
       <c r="AO169" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="170" spans="41:41">
       <c r="AO170" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="171" spans="41:41">
       <c r="AO171" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="172" spans="41:41">
       <c r="AO172" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="173" spans="41:41">
       <c r="AO173" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="174" spans="41:41">
       <c r="AO174" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="175" spans="41:41">
       <c r="AO175" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="176" spans="41:41">
       <c r="AO176" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="177" spans="41:41">
       <c r="AO177" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="178" spans="41:41">
       <c r="AO178" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="179" spans="41:41">
       <c r="AO179" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="180" spans="41:41">
       <c r="AO180" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="181" spans="41:41">
       <c r="AO181" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="182" spans="41:41">
       <c r="AO182" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="183" spans="41:41">
       <c r="AO183" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="184" spans="41:41">
       <c r="AO184" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="185" spans="41:41">
       <c r="AO185" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="186" spans="41:41">
       <c r="AO186" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="187" spans="41:41">
       <c r="AO187" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="188" spans="41:41">
       <c r="AO188" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="189" spans="41:41">
       <c r="AO189" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="190" spans="41:41">
       <c r="AO190" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="191" spans="41:41">
       <c r="AO191" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="192" spans="41:41">
       <c r="AO192" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="193" spans="41:41">
       <c r="AO193" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="194" spans="41:41">
       <c r="AO194" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="195" spans="41:41">
       <c r="AO195" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="196" spans="41:41">
       <c r="AO196" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="197" spans="41:41">
       <c r="AO197" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="198" spans="41:41">
       <c r="AO198" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="199" spans="41:41">
       <c r="AO199" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="200" spans="41:41">
       <c r="AO200" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="201" spans="41:41">
       <c r="AO201" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="202" spans="41:41">
       <c r="AO202" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="203" spans="41:41">
       <c r="AO203" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="204" spans="41:41">
       <c r="AO204" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="205" spans="41:41">
       <c r="AO205" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="206" spans="41:41">
       <c r="AO206" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="207" spans="41:41">
       <c r="AO207" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="208" spans="41:41">
       <c r="AO208" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="209" spans="41:41">
       <c r="AO209" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="210" spans="41:41">
       <c r="AO210" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="211" spans="41:41">
       <c r="AO211" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="212" spans="41:41">
       <c r="AO212" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="213" spans="41:41">
       <c r="AO213" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="214" spans="41:41">
       <c r="AO214" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="215" spans="41:41">
       <c r="AO215" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="216" spans="41:41">
       <c r="AO216" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="217" spans="41:41">
       <c r="AO217" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="218" spans="41:41">
       <c r="AO218" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="219" spans="41:41">
       <c r="AO219" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="220" spans="41:41">
       <c r="AO220" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="221" spans="41:41">
       <c r="AO221" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="222" spans="41:41">
       <c r="AO222" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="223" spans="41:41">
       <c r="AO223" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="224" spans="41:41">
       <c r="AO224" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="225" spans="41:41">
       <c r="AO225" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="226" spans="41:41">
       <c r="AO226" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="227" spans="41:41">
       <c r="AO227" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="228" spans="41:41">
       <c r="AO228" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="229" spans="41:41">
       <c r="AO229" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="230" spans="41:41">
       <c r="AO230" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="231" spans="41:41">
       <c r="AO231" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="232" spans="41:41">
       <c r="AO232" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="233" spans="41:41">
       <c r="AO233" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="234" spans="41:41">
       <c r="AO234" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="235" spans="41:41">
       <c r="AO235" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="236" spans="41:41">
       <c r="AO236" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="237" spans="41:41">
       <c r="AO237" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="238" spans="41:41">
       <c r="AO238" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="239" spans="41:41">
       <c r="AO239" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="240" spans="41:41">
       <c r="AO240" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="241" spans="41:41">
       <c r="AO241" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="242" spans="41:41">
       <c r="AO242" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="243" spans="41:41">
       <c r="AO243" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="244" spans="41:41">
       <c r="AO244" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="245" spans="41:41">
       <c r="AO245" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="246" spans="41:41">
       <c r="AO246" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="247" spans="41:41">
       <c r="AO247" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
     <row r="248" spans="41:41">
       <c r="AO248" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="249" spans="41:41">
       <c r="AO249" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
     </row>
     <row r="250" spans="41:41">
       <c r="AO250" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
     </row>
     <row r="251" spans="41:41">
       <c r="AO251" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="252" spans="41:41">
       <c r="AO252" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
     </row>
     <row r="253" spans="41:41">
       <c r="AO253" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="254" spans="41:41">
       <c r="AO254" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="255" spans="41:41">
       <c r="AO255" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="256" spans="41:41">
       <c r="AO256" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="257" spans="41:41">
       <c r="AO257" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="258" spans="41:41">
       <c r="AO258" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="259" spans="41:41">
       <c r="AO259" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="260" spans="41:41">
       <c r="AO260" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="261" spans="41:41">
       <c r="AO261" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="262" spans="41:41">
       <c r="AO262" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="263" spans="41:41">
       <c r="AO263" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="264" spans="41:41">
       <c r="AO264" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="265" spans="41:41">
       <c r="AO265" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="266" spans="41:41">
       <c r="AO266" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="267" spans="41:41">
       <c r="AO267" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="268" spans="41:41">
       <c r="AO268" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="269" spans="41:41">
       <c r="AO269" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="270" spans="41:41">
       <c r="AO270" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="271" spans="41:41">
       <c r="AO271" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
     <row r="272" spans="41:41">
       <c r="AO272" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="273" spans="41:41">
       <c r="AO273" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="274" spans="41:41">
       <c r="AO274" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="275" spans="41:41">
       <c r="AO275" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="276" spans="41:41">
       <c r="AO276" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="277" spans="41:41">
       <c r="AO277" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="278" spans="41:41">
       <c r="AO278" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="279" spans="41:41">
       <c r="AO279" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="280" spans="41:41">
       <c r="AO280" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
     </row>
     <row r="281" spans="41:41">
       <c r="AO281" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="282" spans="41:41">
       <c r="AO282" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="283" spans="41:41">
       <c r="AO283" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="284" spans="41:41">
       <c r="AO284" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="285" spans="41:41">
       <c r="AO285" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="286" spans="41:41">
       <c r="AO286" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="287" spans="41:41">
       <c r="AO287" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="288" spans="41:41">
       <c r="AO288" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="289" spans="41:41">
       <c r="AO289" t="s">
-        <v>678</v>
+        <v>679</v>
+      </c>
+    </row>
+    <row r="290" spans="41:41">
+      <c r="AO290" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="291" spans="41:41">
+      <c r="AO291" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="292" spans="41:41">
+      <c r="AO292" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="293" spans="41:41">
+      <c r="AO293" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="294" spans="41:41">
+      <c r="AO294" t="s">
+        <v>684</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000018/metadata_template_ERC000018.xlsx
+++ b/templates/ERC000018/metadata_template_ERC000018.xlsx
@@ -1219,7 +1219,7 @@
     <t>amount or size of sample collected</t>
   </si>
   <si>
-    <t>(Optional) The total amount or size (volume (ml), mass (g) or area (m2) ) of sample collected. (Units: m3)</t>
+    <t>(Optional) The total amount or size (volume (ml), mass (g) or area (m2) ) of sample collected. (Units: kg)</t>
   </si>
   <si>
     <t>organism count</t>
@@ -2233,7 +2233,7 @@
     <t>host height</t>
   </si>
   <si>
-    <t>(Optional) The height of subject (Units: mm)</t>
+    <t>(Optional) The height of subject (Units: m)</t>
   </si>
   <si>
     <t>host body-mass index</t>
@@ -2617,7 +2617,7 @@
     <t>sample volume or weight for DNA extraction</t>
   </si>
   <si>
-    <t>(Optional) Volume (ml) or mass (g) of total collected sample processed for dna extraction. note: total sample collected should be entered under the term 'sample size'. (Units: ng)</t>
+    <t>(Optional) Volume (ml) or mass (g) of total collected sample processed for dna extraction. note: total sample collected should be entered under the term 'sample size'. (Units: mL)</t>
   </si>
   <si>
     <t>nucleic acid extraction</t>
